--- a/assets/materials_table.xlsx
+++ b/assets/materials_table.xlsx
@@ -2057,8 +2057,10 @@
       <c r="D23" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>109</v>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">迅捷 + 治疗</t>
+        </is>
       </c>
       <c r="F23" s="2" t="s">
         <v>109</v>
